--- a/data/tags/אלבומים חדשים/sites/rotter/2026-05-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי פרץ - כל עולמי EP</v>
+        <v>זהו זה - עונה 8</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24468&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:35</v>
+        <v>09:37</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי פרץ - כל עולמי EP</v>
+        <v>זהו זה - עונה 8</v>
       </c>
     </row>
   </sheetData>
